--- a/docs/sample-outputs/report_invoice_export_q1.xlsx
+++ b/docs/sample-outputs/report_invoice_export_q1.xlsx
@@ -14,7 +14,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+  <si>
+    <t>REFERENCE_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>DUPLICATE_CONTENT</t>
+  </si>
+  <si>
+    <t>DUPLICATE_ID</t>
+  </si>
+  <si>
+    <t>Assignment ID 'TAS-004' not found. File could not be saved to database.</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('lim wei jie', '2025-01-31', 'paid', '2025-02-05') already exists at row 1.</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-001' already exists (first seen at row 1).</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-003' already exists (first seen at row 3).</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('muhammad hafiz', '2025-02-28', 'paid', '2025-03-03') already exists at row 3.</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-002' already exists (first seen at row 2).</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('tan xiu ying', '2025-03-31', 'pending', '') already exists at row 2.</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-007' already exists (first seen at row 7).</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('aisha binte yusof', '2025-07-31', 'paid', '2025-08-02') already exists at row 7.</t>
+  </si>
+  <si>
+    <t>Assignment ID 'TAS-009' not found. File could not be saved to database.</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-008' already exists (first seen at row 8).</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('darren foo', '2025-08-31', 'paid', '2025-09-01') already exists at row 8.</t>
+  </si>
+  <si>
+    <t>ID 'INV-2025-001' already exists (first seen at row 9).</t>
+  </si>
+  <si>
+    <t>Entry with identical details: ('lim wei jie', '2025-01-31', 'paid', '2025-02-05') already exists at row 9.</t>
+  </si>
   <si>
     <t>INV-2025-001</t>
   </si>
@@ -151,9 +202,6 @@
     <t>SGD 75.00</t>
   </si>
   <si>
-    <t>SGD 112.50</t>
-  </si>
-  <si>
     <t>SGD 165.00</t>
   </si>
   <si>
@@ -175,9 +223,6 @@
     <t>PENDING</t>
   </si>
   <si>
-    <t xml:space="preserve">Pending </t>
-  </si>
-  <si>
     <t>2025-02-05</t>
   </si>
   <si>
@@ -211,34 +256,13 @@
     <t>Note trailing space</t>
   </si>
   <si>
-    <t>MISSING_RELATIONSHIP</t>
-  </si>
-  <si>
-    <t>DUPLICATE_ID</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-004' not found. File could not be saved to database.</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-007' not found. File could not be saved to database.</t>
-  </si>
-  <si>
-    <t>ID 'INV-2025-001' already exists (first seen at row 1).</t>
-  </si>
-  <si>
-    <t>ID 'INV-2025-003' already exists (first seen at row 3).</t>
-  </si>
-  <si>
-    <t>ID 'INV-2025-002' already exists (first seen at row 2).</t>
-  </si>
-  <si>
-    <t>ID 'INV-2025-007' already exists (first seen at row 7).</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-009' not found. File could not be saved to database.</t>
-  </si>
-  <si>
-    <t>ID 'INV-2025-008' already exists (first seen at row 8).</t>
+    <t>Row Index</t>
+  </si>
+  <si>
+    <t>Reason Code</t>
+  </si>
+  <si>
+    <t>Error Details</t>
   </si>
   <si>
     <t>Invoice ID</t>
@@ -266,12 +290,6 @@
   </si>
   <si>
     <t>Duration (Hours)</t>
-  </si>
-  <si>
-    <t>Reason Code</t>
-  </si>
-  <si>
-    <t>Error Details</t>
   </si>
 </sst>
 </file>
@@ -641,419 +659,459 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
-    <col min="11" max="11" width="50.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="28.7109375" customWidth="1"/>
+    <col min="12" max="12" width="21.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1">
+        <v>165</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="1">
+        <v>90</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="1">
+        <v>240</v>
+      </c>
+      <c r="I4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="1">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="1">
+        <v>112.5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="1">
-        <v>165</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1">
-        <v>90</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="1">
-        <v>240</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="1">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="1">
-        <v>90</v>
-      </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
+      <c r="H8" s="1">
+        <v>90</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="1">
-        <v>165</v>
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>0</v>
+      <c r="H9" s="1">
+        <v>165</v>
+      </c>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>8</v>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="1">
+        <v>120</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
         <v>32</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="1">
-        <v>120</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="1">
-        <v>135</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1">
-        <v>70</v>
+      <c r="E15" t="s">
+        <v>39</v>
       </c>
       <c r="F15" t="s">
         <v>50</v>
@@ -1061,149 +1119,359 @@
       <c r="G15" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>6</v>
+      <c r="H15" s="1">
+        <v>135</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16">
+        <v>13</v>
       </c>
       <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="1">
+        <v>70</v>
+      </c>
+      <c r="I18" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="1">
+        <v>165</v>
+      </c>
+      <c r="I24" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
         <v>30</v>
       </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" t="s">
-        <v>65</v>
-      </c>
-      <c r="K17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="1">
-        <v>165</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
-      </c>
-      <c r="J20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" t="s">
         <v>69</v>
       </c>
     </row>
